--- a/라벨agent/발주서/생산등록_양식.xlsx
+++ b/라벨agent/발주서/생산등록_양식.xlsx
@@ -449,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -460,7 +460,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>100</v>
+        <v>50000</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
